--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89080D68-06C3-4AAE-95B0-65373B4C4176}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CB354F-BB19-4C31-9BF2-DE9B0AAC7704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
@@ -195,18 +195,6 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Wed Feb 04 18:40:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 18:44:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Feb 04 18:45:32 IST 2026</t>
-  </si>
-  <si>
-    <t>SC</t>
-  </si>
-  <si>
     <t>Payment app+mandatory values+Zip only from non mandatory(auto State)</t>
   </si>
   <si>
@@ -237,18 +225,6 @@
     <t>Payment app+blank mandatory values+fill only non mandatory values(new CAN &amp; new Amount)</t>
   </si>
   <si>
-    <t>Thu Feb 05 17:43:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 17:44:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 23:22:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 23:35:13 IST 2026</t>
-  </si>
-  <si>
     <t>Please enter a valid 10-digit phone number.</t>
   </si>
   <si>
@@ -258,40 +234,64 @@
     <t>Please provide at least an email address or phone number.</t>
   </si>
   <si>
-    <t>Thu Feb 05 23:48:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 23:48:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 23:49:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 23:50:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Feb 05 23:53:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 00:01:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:16:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:20:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:23:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:26:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:30:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Fri Feb 06 19:32:18 IST 2026</t>
+    <t>Tue Feb 17 12:22:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:23:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:25:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:26:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 12:27:23 IST 2026</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 14:46:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 14:47:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 14:52:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 14:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 14:57:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 14:59:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 15:03:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 15:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 15:39:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 15:50:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:08:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:09:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:11:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Feb 17 16:12:25 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -416,7 +416,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -478,7 +478,6 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -824,7 +823,7 @@
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.36328125" style="22" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
     <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
@@ -837,7 +836,7 @@
     <col min="13" max="14" width="14.453125" style="6" customWidth="1" collapsed="1"/>
     <col min="15" max="15" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
     <col min="16" max="16" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="18" max="18" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
     <col min="19" max="27" width="8.7265625" style="6" collapsed="1"/>
     <col min="28" max="16384" width="8.7265625" style="1" collapsed="1"/>
@@ -930,11 +929,11 @@
       <c r="A2" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>52</v>
+      <c r="B2" t="s">
+        <v>74</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -976,10 +975,10 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
@@ -1003,10 +1002,10 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>4</v>
@@ -1031,11 +1030,11 @@
       <c r="A5" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>53</v>
+      <c r="B5" t="s">
+        <v>71</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>4</v>
@@ -1068,7 +1067,7 @@
         <v>123456</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>46</v>
@@ -1084,11 +1083,11 @@
       <c r="A6" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>54</v>
+      <c r="B6" t="s">
+        <v>72</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>4</v>
@@ -1121,7 +1120,7 @@
         <v>123456</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>46</v>
@@ -1138,10 +1137,10 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
@@ -1177,7 +1176,7 @@
         <v>123456</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>46</v>
@@ -1194,10 +1193,10 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>4</v>
@@ -1226,10 +1225,10 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>4</v>
@@ -1255,10 +1254,10 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
@@ -1312,7 +1311,9 @@
     <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
     <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
     <col min="14" max="14" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="21" width="8.7265625" style="6" collapsed="1"/>
+    <col min="15" max="16" width="8.7265625" style="6" collapsed="1"/>
+    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="18" max="21" width="8.7265625" style="6" collapsed="1"/>
     <col min="22" max="22" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
     <col min="23" max="23" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
     <col min="24" max="24" width="6" style="6" customWidth="1" collapsed="1"/>
@@ -1414,10 +1415,10 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>4</v>
@@ -1441,7 +1442,7 @@
         <v>1000</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>46</v>
@@ -1461,7 +1462,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1499,7 +1500,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1536,9 +1537,9 @@
         <v>1000</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB5" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB5" s="22" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1547,7 +1548,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1568,7 +1569,7 @@
       <c r="K6" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB6" s="23" t="s">
+      <c r="AB6" s="22" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1577,7 +1578,7 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1601,7 +1602,7 @@
         <v>2</v>
       </c>
       <c r="AB7" s="11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="25" x14ac:dyDescent="0.25">
@@ -1609,7 +1610,7 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1633,7 +1634,7 @@
         <v>1234567890</v>
       </c>
       <c r="AB8" s="11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="25" x14ac:dyDescent="0.25">
@@ -1641,7 +1642,7 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1659,7 +1660,7 @@
         <v>43</v>
       </c>
       <c r="AB9" s="11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="25" x14ac:dyDescent="0.25">
@@ -1667,7 +1668,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1700,7 +1701,7 @@
         <v>1000</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>46</v>
@@ -1712,7 +1713,7 @@
         <v>48</v>
       </c>
       <c r="AB10" s="11" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
@@ -1720,7 +1721,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
@@ -1744,7 +1745,7 @@
         <v>1000</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB11" s="11" t="s">
         <v>36</v>

--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CB354F-BB19-4C31-9BF2-DE9B0AAC7704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4462111-02C8-4505-ACCD-5201003075D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
@@ -234,64 +234,64 @@
     <t>Please provide at least an email address or phone number.</t>
   </si>
   <si>
-    <t>Tue Feb 17 12:22:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:23:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:25:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:26:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 12:27:23 IST 2026</t>
-  </si>
-  <si>
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Tue Feb 17 14:46:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 14:47:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 14:52:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 14:55:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 14:57:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 14:59:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 15:03:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 15:07:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 15:39:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 15:50:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:08:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:09:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:11:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Feb 17 16:12:25 IST 2026</t>
+    <t>Thu Feb 19 15:36:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:21:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:23:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:23:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:25:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:26:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:31:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:33:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:35:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:36:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:38:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:39:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:41:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:45:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:47:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:49:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:51:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:52:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Feb 23 17:53:35 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -930,7 +930,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -975,7 +975,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1002,7 +1002,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1031,7 +1031,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1067,7 +1067,7 @@
         <v>123456</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>46</v>
@@ -1084,7 +1084,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1120,7 +1120,7 @@
         <v>123456</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>46</v>
@@ -1137,7 +1137,7 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1176,7 +1176,7 @@
         <v>123456</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>46</v>
@@ -1225,7 +1225,7 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1254,7 +1254,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1415,7 +1415,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1442,7 +1442,7 @@
         <v>1000</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R2" s="6" t="s">
         <v>46</v>
@@ -1462,7 +1462,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1480,7 +1480,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
@@ -1537,7 +1537,7 @@
         <v>1000</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB5" s="22" t="s">
         <v>37</v>
@@ -1548,7 +1548,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1578,7 +1578,7 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1610,7 +1610,7 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1642,7 +1642,7 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1668,7 +1668,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1701,7 +1701,7 @@
         <v>1000</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>46</v>
@@ -1721,7 +1721,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
@@ -1745,7 +1745,7 @@
         <v>1000</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB11" s="11" t="s">
         <v>36</v>

--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4462111-02C8-4505-ACCD-5201003075D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{B4462111-02C8-4505-ACCD-5201003075D4}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
-    <sheet name="ManualEntryError" sheetId="2" r:id="rId2"/>
+    <sheet name="ManualEntry" r:id="rId1" sheetId="1"/>
+    <sheet name="ManualEntryError" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="125">
   <si>
     <t>Result</t>
   </si>
@@ -292,12 +292,133 @@
   </si>
   <si>
     <t>Mon Feb 23 17:53:35 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thu Mar 12 11:31:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 21:45:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:11:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:12:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:13:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:14:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:14:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:15:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:16:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:16:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:17:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:36:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:37:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:38:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:38:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:39:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:40:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Mar 19 22:41:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 15:40:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:59:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:00:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:01:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:02:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:03:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:03:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:04:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:05:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:05:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:06:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:07:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:07:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:08:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:09:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:10:16 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -413,84 +534,84 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -507,10 +628,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -545,7 +666,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -597,7 +718,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -708,21 +829,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -739,7 +860,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -811,38 +932,38 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AA10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:AB10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="14" width="14.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="19" max="27" width="8.7265625" style="6" collapsed="1"/>
-    <col min="28" max="16384" width="8.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="21" width="15.36328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
+    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
+    <col min="13" max="14" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="18" max="18" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
+    <col min="19" max="27" style="6" width="8.7265625" collapsed="true"/>
+    <col min="28" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
+    <row customFormat="1" ht="25" r="1" s="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -925,12 +1046,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+    <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -970,12 +1091,12 @@
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
     </row>
-    <row r="3" spans="1:27" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="21.5" r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -997,12 +1118,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1026,12 +1147,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="38" r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1079,12 +1200,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="6" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1132,12 +1253,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1188,12 +1309,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1220,12 +1341,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1249,12 +1370,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1281,47 +1402,47 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
-    <hyperlink ref="J4" r:id="rId2" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
-    <hyperlink ref="J5" r:id="rId3" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
-    <hyperlink ref="J7" r:id="rId4" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
-    <hyperlink ref="J8" r:id="rId5" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
-    <hyperlink ref="J9" r:id="rId6" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
+    <hyperlink r:id="rId1" ref="J2" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
+    <hyperlink r:id="rId2" ref="J4" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
+    <hyperlink r:id="rId3" ref="J5" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
+    <hyperlink r:id="rId4" ref="J7" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
+    <hyperlink r:id="rId5" ref="J8" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
+    <hyperlink r:id="rId6" ref="J9" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AB11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="8.7265625" style="6" collapsed="1"/>
-    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="21" width="8.7265625" style="6" collapsed="1"/>
-    <col min="22" max="22" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6" style="6" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="5.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="29" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
+    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="6" width="13.453125" collapsed="true"/>
+    <col min="15" max="16" style="6" width="8.7265625" collapsed="true"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="18" max="21" style="6" width="8.7265625" collapsed="true"/>
+    <col min="22" max="22" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="6" width="5.90625" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
+    <col min="29" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -1410,12 +1531,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>115</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1457,12 +1578,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1475,12 +1596,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
@@ -1495,12 +1616,12 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1543,12 +1664,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1573,12 +1694,12 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1605,12 +1726,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1637,12 +1758,12 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1663,12 +1784,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1721,7 +1842,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>124</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
@@ -1753,11 +1874,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
-    <hyperlink ref="J6" r:id="rId2" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
-    <hyperlink ref="J7" r:id="rId3" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
+    <hyperlink r:id="rId1" ref="J5" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
+    <hyperlink r:id="rId2" ref="J6" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
+    <hyperlink r:id="rId3" ref="J7" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{B4462111-02C8-4505-ACCD-5201003075D4}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{9C2B76EA-102D-41A2-84E6-B17E803E3469}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
     <sheet name="ManualEntry" r:id="rId1" sheetId="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="105">
   <si>
     <t>Result</t>
   </si>
@@ -237,181 +237,121 @@
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Thu Feb 19 15:36:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:21:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:23:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:23:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:25:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:26:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:31:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:33:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:35:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:36:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:38:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:39:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:41:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:45:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:47:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:49:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:51:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:52:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Feb 23 17:53:35 IST 2026</t>
+    <t>Wed Mar 25 17:59:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:00:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:00:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:01:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:02:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:03:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:04:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:04:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:05:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:05:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:06:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:07:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:07:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:08:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:08:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:09:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:09:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 18:10:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:20:31 IST 2026</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Thu Mar 12 11:31:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 21:45:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:11:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:12:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:13:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:14:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:14:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:15:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:16:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:16:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:17:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:36:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:37:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:38:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:38:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:39:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:39:58 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:40:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Mar 19 22:41:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 15:40:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:59:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:00:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:00:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:01:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:02:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:03:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:03:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:04:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:04:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:05:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:05:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:06:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:07:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:07:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:08:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:08:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:09:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:09:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:10:16 IST 2026</t>
+    <t>Tue Apr 21 19:24:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:25:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:25:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:26:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:27:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:28:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:30:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Apr 21 19:31:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:32:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:33:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:34:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:35:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:35:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:36:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:37:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:37:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:38:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 23 15:39:03 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +991,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -1096,7 +1036,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1123,7 +1063,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1152,7 +1092,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1205,7 +1145,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1258,7 +1198,7 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1314,7 +1254,7 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1346,7 +1286,7 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1375,7 +1315,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1536,7 +1476,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1583,7 +1523,7 @@
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1601,7 +1541,7 @@
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
@@ -1621,7 +1561,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1669,7 +1609,7 @@
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1699,7 +1639,7 @@
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1731,7 +1671,7 @@
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1763,7 +1703,7 @@
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1789,7 +1729,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1842,7 +1782,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>

--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{9C2B76EA-102D-41A2-84E6-B17E803E3469}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8E5B64-C525-4ACA-9408-2D326808402B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry" r:id="rId1" sheetId="1"/>
-    <sheet name="ManualEntryError" r:id="rId2" sheetId="2"/>
+    <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
+    <sheet name="ManualEntryError" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="91">
   <si>
     <t>Result</t>
   </si>
@@ -237,128 +237,85 @@
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Wed Mar 25 17:59:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:00:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:00:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:01:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:02:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:03:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:04:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:04:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:05:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:05:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:06:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:07:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:07:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:08:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:08:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:09:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:09:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 18:10:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:20:31 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:24:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:25:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:25:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:26:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:27:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:28:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:29:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:30:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Apr 21 19:31:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:32:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:33:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:34:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:35:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:35:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:36:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:37:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:37:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:38:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 23 15:39:03 IST 2026</t>
+    <t>Thu Apr 30 14:34:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:35:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:35:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:36:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:37:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:37:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:38:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:40:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:40:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:41:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:41:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:42:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:43:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:43:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:44:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:45:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Apr 30 14:45:44 IST 2026</t>
+  </si>
+  <si>
+    <t>DueDate</t>
+  </si>
+  <si>
+    <t>Payment app+Mandatory+nonMandatory+email+phone+Due Date</t>
+  </si>
+  <si>
+    <t>Payment app+Mandatory+nonMandatory+email+phone+ no Due Date</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Tue May 05 20:22:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue May 05 20:23:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 06 17:50:07 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -474,84 +431,84 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -568,10 +525,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -606,7 +563,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -658,7 +615,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -769,21 +726,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -800,7 +757,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -872,38 +829,39 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AB10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="21" width="15.36328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
-    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
-    <col min="13" max="14" customWidth="true" style="6" width="14.453125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="18" max="18" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
-    <col min="19" max="27" style="6" width="8.7265625" collapsed="true"/>
-    <col min="28" max="16384" style="1" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="20" max="28" width="8.7265625" style="6" collapsed="1"/>
+    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="25" r="1" s="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -941,57 +899,60 @@
         <v>21</v>
       </c>
       <c r="M1" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="18" t="s">
+      <c r="R1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="U1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="V1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="14" t="s">
+      <c r="W1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="14" t="s">
+      <c r="X1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="14" t="s">
+      <c r="Y1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="14" t="s">
+      <c r="Z1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="14" t="s">
+      <c r="AA1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="14" t="s">
+      <c r="AB1" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -1023,20 +984,21 @@
       <c r="R2" s="8"/>
       <c r="S2" s="8"/>
       <c r="T2" s="8"/>
-      <c r="U2" s="9"/>
+      <c r="U2" s="8"/>
       <c r="V2" s="9"/>
       <c r="W2" s="9"/>
       <c r="X2" s="9"/>
       <c r="Y2" s="9"/>
       <c r="Z2" s="9"/>
       <c r="AA2" s="9"/>
-    </row>
-    <row customHeight="1" ht="21.5" r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB2" s="9"/>
+    </row>
+    <row r="3" spans="1:28" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1058,12 +1020,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row ht="25" r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1087,12 +1049,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row customHeight="1" ht="38" r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1115,37 +1077,37 @@
       <c r="L5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="6">
+      <c r="Q5" s="6">
         <v>123456</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="S5" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="T5" s="6" t="s">
+      <c r="U5" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1168,37 +1130,37 @@
       <c r="L6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="O6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P6" s="6">
+      <c r="Q6" s="6">
         <v>123456</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="R6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="S6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="T6" s="6" t="s">
+      <c r="U6" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1224,37 +1186,37 @@
       <c r="L7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="O7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="P7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P7" s="6">
+      <c r="Q7" s="6">
         <v>123456</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="T7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="U7" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1277,16 +1239,16 @@
       <c r="K8" s="6">
         <v>1234567890</v>
       </c>
-      <c r="P8" s="6">
+      <c r="Q8" s="6">
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1306,16 +1268,16 @@
       <c r="J9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="P9" s="6">
+      <c r="Q9" s="6">
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1335,54 +1297,174 @@
       <c r="K10" s="6">
         <v>1234567890</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>22201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K11" s="6">
+        <v>1234567890</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="6">
+        <v>123456</v>
+      </c>
+      <c r="R11" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="U11" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K12" s="6">
+        <v>1234567890</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>123456</v>
+      </c>
+      <c r="R12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="S12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="U12" s="6" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J2" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
-    <hyperlink r:id="rId2" ref="J4" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
-    <hyperlink r:id="rId3" ref="J5" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
-    <hyperlink r:id="rId4" ref="J7" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
-    <hyperlink r:id="rId5" ref="J8" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
-    <hyperlink r:id="rId6" ref="J9" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
+    <hyperlink ref="J7" r:id="rId4" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
+    <hyperlink ref="J8" r:id="rId5" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
+    <hyperlink ref="J9" r:id="rId6" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
+    <hyperlink ref="J11" r:id="rId7" xr:uid="{E4EA5532-5BA0-42CD-A768-5DEFD35BC93F}"/>
+    <hyperlink ref="J12" r:id="rId8" xr:uid="{6E3D0AE5-F8C0-4CAA-B08A-94225D16564A}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AC11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
-    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="13.453125" collapsed="true"/>
-    <col min="15" max="16" style="6" width="8.7265625" collapsed="true"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="18" max="21" style="6" width="8.7265625" collapsed="true"/>
-    <col min="22" max="22" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="6" width="6.0" collapsed="true"/>
-    <col min="25" max="25" customWidth="true" style="6" width="5.90625" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
-    <col min="29" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="13.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="16" width="8.7265625" style="6" collapsed="1"/>
+    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="18" max="21" width="8.7265625" style="6" collapsed="1"/>
+    <col min="22" max="22" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="23" max="23" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="6" style="6" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="5.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
+    <col min="29" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
@@ -1471,12 +1553,12 @@
         <v>35</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1518,12 +1600,12 @@
         <v>36</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1536,12 +1618,12 @@
         <v>36</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
@@ -1556,12 +1638,12 @@
         <v>36</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1604,12 +1686,12 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="25" r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1634,12 +1716,12 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="25" r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1666,12 +1748,12 @@
         <v>62</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1698,12 +1780,12 @@
         <v>63</v>
       </c>
     </row>
-    <row ht="25" r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1724,12 +1806,12 @@
         <v>64</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1782,7 +1864,7 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
@@ -1814,11 +1896,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J5" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
-    <hyperlink r:id="rId2" ref="J6" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
-    <hyperlink r:id="rId3" ref="J7" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
+    <hyperlink ref="J6" r:id="rId2" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
+    <hyperlink ref="J7" r:id="rId3" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8E5B64-C525-4ACA-9408-2D326808402B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AB3C81-EB98-4362-AB9D-65E60E68A71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="91">
   <si>
     <t>Result</t>
   </si>
@@ -261,9 +261,6 @@
     <t>Thu Apr 30 14:39:22 IST 2026</t>
   </si>
   <si>
-    <t>Thu Apr 30 14:40:03 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Apr 30 14:40:48 IST 2026</t>
   </si>
   <si>
@@ -285,9 +282,6 @@
     <t>Thu Apr 30 14:44:28 IST 2026</t>
   </si>
   <si>
-    <t>Thu Apr 30 14:45:02 IST 2026</t>
-  </si>
-  <si>
     <t>Thu Apr 30 14:45:44 IST 2026</t>
   </si>
   <si>
@@ -310,6 +304,12 @@
   </si>
   <si>
     <t>Wed May 06 17:50:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 15:18:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon May 11 15:21:30 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
         <v>21</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>8</v>
@@ -952,7 +952,7 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -1306,10 +1306,10 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
@@ -1365,10 +1365,10 @@
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -1392,7 +1392,7 @@
         <v>50</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>45</v>
@@ -1437,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
@@ -1452,22 +1452,23 @@
     <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
     <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
     <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="16" width="8.7265625" style="6" collapsed="1"/>
-    <col min="17" max="17" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="18" max="21" width="8.7265625" style="6" collapsed="1"/>
-    <col min="22" max="22" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="23" max="23" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6" style="6" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="5.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="29" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="22" width="8.7265625" style="6" collapsed="1"/>
+    <col min="23" max="23" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="5.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
+    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1505,60 +1506,63 @@
         <v>21</v>
       </c>
       <c r="M1" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="N1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="P1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="Q1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="R1" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="S1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="T1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="U1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="15" t="s">
+      <c r="V1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="X1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="Y1" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="15" t="s">
+      <c r="Z1" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="15" t="s">
+      <c r="AA1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="15" t="s">
+      <c r="AB1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="13" t="s">
+      <c r="AC1" s="13" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1572,40 +1576,43 @@
       <c r="L2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P2" s="6">
+      <c r="Q2" s="6">
         <v>1000</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AB2" s="11" t="s">
+      <c r="AC2" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
@@ -1614,16 +1621,16 @@
         <v>4</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="AB3" s="11" t="s">
+      <c r="AC3" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
@@ -1634,16 +1641,16 @@
       <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="11" t="s">
+      <c r="AC4" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1667,31 +1674,31 @@
       <c r="L5" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P5" s="6">
+      <c r="Q5" s="6">
         <v>1000</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AB5" s="22" t="s">
+      <c r="AC5" s="22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1712,16 +1719,16 @@
       <c r="K6" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB6" s="22" t="s">
+      <c r="AC6" s="22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
@@ -1744,16 +1751,16 @@
       <c r="K7" s="6">
         <v>2</v>
       </c>
-      <c r="AB7" s="11" t="s">
+      <c r="AC7" s="11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
@@ -1776,16 +1783,16 @@
       <c r="K8" s="6">
         <v>1234567890</v>
       </c>
-      <c r="AB8" s="11" t="s">
+      <c r="AC8" s="11" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
@@ -1802,16 +1809,16 @@
       <c r="I9" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="AB9" s="11" t="s">
+      <c r="AC9" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
@@ -1831,40 +1838,40 @@
       <c r="L10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="O10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="P10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>1000</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="R10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="R10" s="6" t="s">
+      <c r="S10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="T10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="T10" s="6" t="s">
+      <c r="U10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="AB10" s="11" t="s">
+      <c r="AC10" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
@@ -1875,22 +1882,22 @@
       <c r="L11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="O11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="P11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="P11" s="6">
+      <c r="Q11" s="6">
         <v>1000</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="R11" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AB11" s="11" t="s">
+      <c r="AC11" s="11" t="s">
         <v>36</v>
       </c>
     </row>

--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4AB3C81-EB98-4362-AB9D-65E60E68A71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{F4AB3C81-EB98-4362-AB9D-65E60E68A71A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
-    <sheet name="ManualEntryError" sheetId="2" r:id="rId2"/>
+    <sheet name="ManualEntry" r:id="rId1" sheetId="1"/>
+    <sheet name="ManualEntryError" r:id="rId2" sheetId="2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="104">
   <si>
     <t>Result</t>
   </si>
@@ -310,12 +310,52 @@
   </si>
   <si>
     <t>Mon May 11 15:21:30 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Wed May 20 18:41:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:41:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:43:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:43:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:44:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:45:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:46:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:46:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:47:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:47:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed May 20 18:59:04 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -431,84 +471,84 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -525,10 +565,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -563,7 +603,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -615,7 +655,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -726,21 +766,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -757,7 +797,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -829,39 +869,39 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AB12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="20" max="28" width="8.7265625" style="6" collapsed="1"/>
-    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="21" width="15.36328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
+    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
+    <col min="14" max="15" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
+    <col min="20" max="28" style="6" width="8.7265625" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
+    <row customFormat="1" ht="25" r="1" s="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -947,12 +987,12 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:28" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
+    <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -993,12 +1033,12 @@
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
     </row>
-    <row r="3" spans="1:28" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="21.5" r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1020,12 +1060,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1049,12 +1089,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="38" r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1102,12 +1142,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1155,12 +1195,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1211,12 +1251,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1243,12 +1283,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1272,12 +1312,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1301,12 +1341,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>83</v>
@@ -1360,12 +1400,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>84</v>
@@ -1422,50 +1462,50 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J2" r:id="rId1" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
-    <hyperlink ref="J4" r:id="rId2" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
-    <hyperlink ref="J5" r:id="rId3" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
-    <hyperlink ref="J7" r:id="rId4" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
-    <hyperlink ref="J8" r:id="rId5" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
-    <hyperlink ref="J9" r:id="rId6" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
-    <hyperlink ref="J11" r:id="rId7" xr:uid="{E4EA5532-5BA0-42CD-A768-5DEFD35BC93F}"/>
-    <hyperlink ref="J12" r:id="rId8" xr:uid="{6E3D0AE5-F8C0-4CAA-B08A-94225D16564A}"/>
+    <hyperlink r:id="rId1" ref="J2" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
+    <hyperlink r:id="rId2" ref="J4" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
+    <hyperlink r:id="rId3" ref="J5" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
+    <hyperlink r:id="rId4" ref="J7" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
+    <hyperlink r:id="rId5" ref="J8" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
+    <hyperlink r:id="rId6" ref="J9" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
+    <hyperlink r:id="rId7" ref="J11" xr:uid="{E4EA5532-5BA0-42CD-A768-5DEFD35BC93F}"/>
+    <hyperlink r:id="rId8" ref="J12" xr:uid="{6E3D0AE5-F8C0-4CAA-B08A-94225D16564A}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AC11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
-    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="22" width="8.7265625" style="6" collapsed="1"/>
-    <col min="23" max="23" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="5.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
+    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="6" width="13.453125" collapsed="true"/>
+    <col min="16" max="17" style="6" width="8.7265625" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="22" style="6" width="8.7265625" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="6" width="5.90625" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
+    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -1557,12 +1597,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
+    <row ht="37.5" r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
@@ -1607,7 +1647,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -1625,7 +1665,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
@@ -1645,7 +1685,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1693,7 +1733,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1723,7 +1763,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -1755,7 +1795,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
@@ -1787,7 +1827,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1813,7 +1853,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1903,11 +1943,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="J5" r:id="rId1" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
-    <hyperlink ref="J6" r:id="rId2" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
-    <hyperlink ref="J7" r:id="rId3" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
+    <hyperlink r:id="rId1" ref="J5" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
+    <hyperlink r:id="rId2" ref="J6" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
+    <hyperlink r:id="rId3" ref="J7" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{F4AB3C81-EB98-4362-AB9D-65E60E68A71A}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F549C55-2923-4FB9-9A8D-349B792D06F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="1" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="ManualEntry" r:id="rId1" sheetId="1"/>
-    <sheet name="ManualEntryError" r:id="rId2" sheetId="2"/>
+    <sheet name="ManualEntry" sheetId="1" r:id="rId1"/>
+    <sheet name="ManualEntryError" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>Result</t>
   </si>
@@ -237,54 +237,6 @@
     <t>South Carolina</t>
   </si>
   <si>
-    <t>Thu Apr 30 14:34:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:35:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:35:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:36:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:37:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:37:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:38:30 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:39:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:40:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:41:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:41:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:42:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:43:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:43:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:44:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Apr 30 14:45:44 IST 2026</t>
-  </si>
-  <si>
     <t>DueDate</t>
   </si>
   <si>
@@ -297,65 +249,76 @@
     <t>N</t>
   </si>
   <si>
-    <t>Tue May 05 20:22:06 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue May 05 20:23:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 06 17:50:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon May 11 15:18:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon May 11 15:21:30 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed May 20 18:41:13 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:41:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:42:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:43:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:43:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:44:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:45:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:46:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:46:37 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:47:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:47:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed May 20 18:59:04 IST 2026</t>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:55:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:56:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:57:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:57:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:58:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 03:59:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:00:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:01:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:02:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 04:03:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:47:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:48:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:49:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:51:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:53:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:54:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:54:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:55:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 22:56:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 23:05:44 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -471,84 +434,84 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
-    <xf applyAlignment="0" applyBorder="0" applyFill="0" applyNumberFormat="0" applyProtection="0" borderId="0" fillId="0" fontId="4" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="2" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="3" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="2" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="6" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle builtinId="8" name="Hyperlink" xfId="1"/>
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -565,10 +528,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -603,7 +566,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -655,7 +618,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -766,21 +729,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -797,7 +760,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -869,39 +832,39 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AC12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="21" width="15.36328125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
-    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
-    <col min="14" max="15" customWidth="true" style="6" width="14.453125" collapsed="true"/>
-    <col min="16" max="16" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
-    <col min="17" max="17" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="19" max="19" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
-    <col min="20" max="28" style="6" width="8.7265625" collapsed="true"/>
-    <col min="29" max="16384" style="1" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
+    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="19" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="20" max="28" width="8.7265625" style="6" collapsed="1"/>
+    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row customFormat="1" ht="25" r="1" s="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -939,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>8</v>
@@ -987,12 +950,12 @@
         <v>28</v>
       </c>
     </row>
-    <row customFormat="1" customHeight="1" ht="19" r="2" s="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -1033,12 +996,12 @@
       <c r="AA2" s="9"/>
       <c r="AB2" s="9"/>
     </row>
-    <row customHeight="1" ht="21.5" r="3" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1060,12 +1023,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row ht="25" r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1089,12 +1052,12 @@
         <v>1234567890</v>
       </c>
     </row>
-    <row customHeight="1" ht="38" r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1142,12 +1105,12 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1195,12 +1158,12 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1251,12 +1214,12 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1283,12 +1246,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1312,12 +1275,12 @@
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1341,15 +1304,15 @@
         <v>22201</v>
       </c>
     </row>
-    <row ht="37.5" r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>4</v>
@@ -1400,15 +1363,15 @@
         <v>48</v>
       </c>
     </row>
-    <row ht="37.5" r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>4</v>
@@ -1432,7 +1395,7 @@
         <v>50</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>45</v>
@@ -1462,50 +1425,50 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J2" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
-    <hyperlink r:id="rId2" ref="J4" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
-    <hyperlink r:id="rId3" ref="J5" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
-    <hyperlink r:id="rId4" ref="J7" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
-    <hyperlink r:id="rId5" ref="J8" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
-    <hyperlink r:id="rId6" ref="J9" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
-    <hyperlink r:id="rId7" ref="J11" xr:uid="{E4EA5532-5BA0-42CD-A768-5DEFD35BC93F}"/>
-    <hyperlink r:id="rId8" ref="J12" xr:uid="{6E3D0AE5-F8C0-4CAA-B08A-94225D16564A}"/>
+    <hyperlink ref="J2" r:id="rId1" xr:uid="{742F3F73-E85A-4FCF-8C7C-C1600E23D754}"/>
+    <hyperlink ref="J4" r:id="rId2" xr:uid="{CF8BFE12-A940-4AA8-89E5-909545A781DB}"/>
+    <hyperlink ref="J5" r:id="rId3" xr:uid="{C88919CB-0AC0-489E-8BBE-E6060EF3457D}"/>
+    <hyperlink ref="J7" r:id="rId4" xr:uid="{B9848D99-3F02-4B1F-B147-DEC60651F43B}"/>
+    <hyperlink ref="J8" r:id="rId5" xr:uid="{FDA63C53-C5A4-429D-B203-33CB3003E9B2}"/>
+    <hyperlink ref="J9" r:id="rId6" xr:uid="{4707D785-3286-488B-9C77-6EC977F6DD2D}"/>
+    <hyperlink ref="J11" r:id="rId7" xr:uid="{E4EA5532-5BA0-42CD-A768-5DEFD35BC93F}"/>
+    <hyperlink ref="J12" r:id="rId8" xr:uid="{6E3D0AE5-F8C0-4CAA-B08A-94225D16564A}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AD11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
-    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
-    <col min="14" max="14" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
-    <col min="15" max="15" customWidth="true" style="6" width="13.453125" collapsed="true"/>
-    <col min="16" max="17" style="6" width="8.7265625" collapsed="true"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
-    <col min="19" max="22" style="6" width="8.7265625" collapsed="true"/>
-    <col min="23" max="23" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="24" max="24" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
-    <col min="25" max="25" customWidth="true" style="6" width="6.0" collapsed="true"/>
-    <col min="26" max="26" customWidth="true" style="6" width="5.90625" collapsed="true"/>
-    <col min="27" max="27" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
-    <col min="28" max="28" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
-    <col min="29" max="29" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
-    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
+    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
+    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="19" max="22" width="8.7265625" style="6" collapsed="1"/>
+    <col min="23" max="23" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
+    <col min="26" max="26" width="5.90625" style="6" customWidth="1" collapsed="1"/>
+    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
+    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
+    <col min="29" max="29" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
+    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -1546,7 +1509,7 @@
         <v>21</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>8</v>
@@ -1597,19 +1560,16 @@
         <v>35</v>
       </c>
     </row>
-    <row ht="37.5" r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="E2" s="5" t="s">
         <v>6</v>
       </c>
@@ -1647,37 +1607,31 @@
         <v>36</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="E3" s="12"/>
       <c r="AC3" s="11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1685,12 +1639,12 @@
         <v>36</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1733,12 +1687,12 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="25" r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1763,19 +1717,16 @@
         <v>37</v>
       </c>
     </row>
-    <row ht="25" r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="E7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1795,19 +1746,16 @@
         <v>62</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="E8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1827,19 +1775,16 @@
         <v>63</v>
       </c>
     </row>
-    <row ht="25" r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="E9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1853,18 +1798,15 @@
         <v>64</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>4</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>6</v>
@@ -1911,14 +1853,11 @@
         <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="L11" s="6" t="s">
         <v>50</v>
       </c>
@@ -1943,11 +1882,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="J5" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
-    <hyperlink r:id="rId2" ref="J6" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
-    <hyperlink r:id="rId3" ref="J7" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
+    <hyperlink ref="J5" r:id="rId1" xr:uid="{588BBDB7-5B95-4FB9-AD9C-36AAC3C41943}"/>
+    <hyperlink ref="J6" r:id="rId2" xr:uid="{CE0F2039-EED1-4DB0-83C0-2B84DB370934}"/>
+    <hyperlink ref="J7" r:id="rId3" xr:uid="{1B3C72AA-06CB-4051-818C-C62CA26213EB}"/>
   </hyperlinks>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId4"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/ManualEntry.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="111">
   <si>
     <t>Result</t>
   </si>
@@ -313,12 +313,70 @@
   </si>
   <si>
     <t>Thu Jun 18 23:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:49:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:50:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:51:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:51:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:52:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:53:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:54:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:55:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:55:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:56:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 16:57:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:08:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:10:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:11:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:13:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:15:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:16:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:18:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:20:00 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -843,25 +901,25 @@
   <dimension ref="A1:AB12"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.26953125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.36328125" style="21" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="31.26953125" style="4" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.08984375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="15" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="5.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="9" width="10.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="17.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="11.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="15" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="15" width="14.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="7.81640625" style="6" customWidth="1" collapsed="1"/>
-    <col min="17" max="17" width="9.1796875" style="6" customWidth="1" collapsed="1"/>
-    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="19" width="8.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="20" max="28" width="8.7265625" style="6" collapsed="1"/>
-    <col min="29" max="16384" width="8.7265625" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="6.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="21" width="15.36328125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="4" width="31.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="8.08984375" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="15.0" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="5.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="8.1796875" collapsed="true"/>
+    <col min="8" max="9" customWidth="true" style="6" width="10.36328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="17.7265625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="11.90625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="15.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
+    <col min="14" max="15" customWidth="true" style="6" width="14.453125" collapsed="true"/>
+    <col min="16" max="16" customWidth="true" style="6" width="7.81640625" collapsed="true"/>
+    <col min="17" max="17" customWidth="true" style="6" width="9.1796875" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="19" customWidth="true" style="6" width="8.54296875" collapsed="true"/>
+    <col min="20" max="28" style="6" width="8.7265625" collapsed="true"/>
+    <col min="29" max="16384" style="1" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" s="3" customFormat="1" ht="25" x14ac:dyDescent="0.25">
@@ -951,11 +1009,11 @@
       </c>
     </row>
     <row r="2" spans="1:28" s="3" customFormat="1" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
-        <v>71</v>
+      <c r="B2" t="s" s="21">
+        <v>92</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>55</v>
@@ -997,11 +1055,11 @@
       <c r="AB2" s="9"/>
     </row>
     <row r="3" spans="1:28" ht="21.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
-        <v>72</v>
+      <c r="B3" t="s" s="21">
+        <v>93</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>56</v>
@@ -1024,11 +1082,11 @@
       </c>
     </row>
     <row r="4" spans="1:28" ht="25" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B4" t="s">
-        <v>73</v>
+      <c r="B4" t="s" s="21">
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>57</v>
@@ -1053,11 +1111,11 @@
       </c>
     </row>
     <row r="5" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B5" t="s">
-        <v>74</v>
+      <c r="B5" t="s" s="21">
+        <v>95</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>60</v>
@@ -1106,11 +1164,11 @@
       </c>
     </row>
     <row r="6" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B6" t="s">
-        <v>75</v>
+      <c r="B6" t="s" s="21">
+        <v>96</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>58</v>
@@ -1159,11 +1217,11 @@
       </c>
     </row>
     <row r="7" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B7" t="s">
-        <v>76</v>
+      <c r="B7" t="s" s="21">
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>59</v>
@@ -1215,11 +1273,11 @@
       </c>
     </row>
     <row r="8" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
-        <v>77</v>
+      <c r="B8" t="s" s="21">
+        <v>98</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>52</v>
@@ -1247,11 +1305,11 @@
       </c>
     </row>
     <row r="9" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
-        <v>78</v>
+      <c r="B9" t="s" s="21">
+        <v>99</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>53</v>
@@ -1276,11 +1334,11 @@
       </c>
     </row>
     <row r="10" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B10" t="s">
-        <v>79</v>
+      <c r="B10" t="s" s="21">
+        <v>100</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>54</v>
@@ -1305,11 +1363,11 @@
       </c>
     </row>
     <row r="11" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
-        <v>80</v>
+      <c r="B11" t="s" s="21">
+        <v>101</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>67</v>
@@ -1364,11 +1422,11 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="B12" t="s">
-        <v>81</v>
+      <c r="B12" t="s" s="21">
+        <v>102</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>68</v>
@@ -1443,32 +1501,32 @@
   <dimension ref="A1:AC11"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="15.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="36" style="11" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="6" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="11.36328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="10.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="16.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12" style="6" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="16" style="6" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="11.7265625" style="6" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="15" max="15" width="13.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="16" max="17" width="8.7265625" style="6" collapsed="1"/>
-    <col min="18" max="18" width="13.90625" style="6" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="19" max="22" width="8.7265625" style="6" collapsed="1"/>
-    <col min="23" max="23" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="24" max="24" width="6.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="25" max="25" width="6" style="6" customWidth="1" collapsed="1"/>
-    <col min="26" max="26" width="5.90625" style="6" customWidth="1" collapsed="1"/>
-    <col min="27" max="27" width="5.6328125" style="6" customWidth="1" collapsed="1"/>
-    <col min="28" max="28" width="6.54296875" style="6" customWidth="1" collapsed="1"/>
-    <col min="29" max="29" width="47.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="30" max="16384" width="8.7265625" style="6" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="6" width="7.26953125" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="6" width="15.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="11" width="36.0" collapsed="true"/>
+    <col min="4" max="4" style="6" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="6" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="6" width="9.36328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="6" width="11.36328125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="6" width="10.7265625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="6" width="10.54296875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="6" width="16.453125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="6" width="12.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="6" width="16.0" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="6" width="11.7265625" collapsed="true"/>
+    <col min="14" max="14" customWidth="true" style="6" width="13.26953125" collapsed="true"/>
+    <col min="15" max="15" customWidth="true" style="6" width="13.453125" collapsed="true"/>
+    <col min="16" max="17" style="6" width="8.7265625" collapsed="true"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="6" width="13.90625" collapsed="true"/>
+    <col min="19" max="22" style="6" width="8.7265625" collapsed="true"/>
+    <col min="23" max="23" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="24" max="24" customWidth="true" style="6" width="6.26953125" collapsed="true"/>
+    <col min="25" max="25" customWidth="true" style="6" width="6.0" collapsed="true"/>
+    <col min="26" max="26" customWidth="true" style="6" width="5.90625" collapsed="true"/>
+    <col min="27" max="27" customWidth="true" style="6" width="5.6328125" collapsed="true"/>
+    <col min="28" max="28" customWidth="true" style="6" width="6.54296875" collapsed="true"/>
+    <col min="29" max="29" customWidth="true" style="11" width="47.08984375" collapsed="true"/>
+    <col min="30" max="16384" style="6" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
@@ -1561,10 +1619,10 @@
       </c>
     </row>
     <row r="2" spans="1:29" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="6">
         <v>82</v>
       </c>
       <c r="C2" s="11" t="s">
@@ -1608,10 +1666,10 @@
       </c>
     </row>
     <row r="3" spans="1:29" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="6">
         <v>83</v>
       </c>
       <c r="C3" s="11" t="s">
@@ -1623,10 +1681,10 @@
       </c>
     </row>
     <row r="4" spans="1:29" ht="13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="6">
         <v>84</v>
       </c>
       <c r="C4" s="11" t="s">
@@ -1640,11 +1698,11 @@
       </c>
     </row>
     <row r="5" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="6">
         <v>70</v>
       </c>
-      <c r="B5" t="s">
-        <v>91</v>
+      <c r="B5" t="s" s="6">
+        <v>109</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>38</v>
@@ -1688,11 +1746,11 @@
       </c>
     </row>
     <row r="6" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="6">
         <v>70</v>
       </c>
-      <c r="B6" t="s">
-        <v>85</v>
+      <c r="B6" t="s" s="6">
+        <v>110</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>39</v>
@@ -1718,10 +1776,10 @@
       </c>
     </row>
     <row r="7" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="6">
         <v>86</v>
       </c>
       <c r="C7" s="11" t="s">
@@ -1747,10 +1805,10 @@
       </c>
     </row>
     <row r="8" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="A8" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="6">
         <v>87</v>
       </c>
       <c r="C8" s="11" t="s">
@@ -1776,10 +1834,10 @@
       </c>
     </row>
     <row r="9" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="6">
         <v>88</v>
       </c>
       <c r="C9" s="11" t="s">
@@ -1799,10 +1857,10 @@
       </c>
     </row>
     <row r="10" spans="1:29" ht="25" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="6">
         <v>89</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -1849,10 +1907,10 @@
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="A11" t="s" s="6">
         <v>51</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="6">
         <v>90</v>
       </c>
       <c r="C11" s="11" t="s">
